--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_OW_Part2.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_OW_Part2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDDB69CF-81D5-4FAD-88B1-9262C0484A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F1CC51-1888-4A50-9A5D-F5B21D936DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RQ8 for OW ADMs variable defint" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="82">
   <si>
     <t>Variables</t>
   </si>
@@ -169,9 +169,6 @@
     <t>Tagging accuracy overall</t>
   </si>
   <si>
-    <t>Tag expectant patient as expectant?</t>
-  </si>
-  <si>
     <t>Order engaged by participant</t>
   </si>
   <si>
@@ -184,23 +181,13 @@
     <t>Levels</t>
   </si>
   <si>
-    <t xml:space="preserve">April2026 desert2 or April2026 urban2
-</t>
-  </si>
-  <si>
     <t>MF1-8 or AF1-8</t>
-  </si>
-  <si>
-    <t>Baseline, Zeroshot, DR Mistral or CR Mistral</t>
   </si>
   <si>
     <t>Patient A or Patient B</t>
   </si>
   <si>
     <t>0.0-1.0</t>
-  </si>
-  <si>
-    <t>Yes/no</t>
   </si>
   <si>
     <t>number</t>
@@ -288,6 +275,16 @@
   </si>
   <si>
     <t>Patient 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April2026 desert2, April2026 urban2, Feb2026 desert2, Feb2026 urban2, June2025 desert2, June2025 urban2
+</t>
+  </si>
+  <si>
+    <t>Yes, No, N/A</t>
+  </si>
+  <si>
+    <t>Tag expectant patient as expectant? N/A - The scenario had no expectant patient</t>
   </si>
 </sst>
 </file>
@@ -995,31 +992,29 @@
         <v>42</v>
       </c>
       <c r="V3" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="X3" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="X3" s="15" t="s">
+      <c r="Y3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="15" t="s">
+    </row>
+    <row r="4" spans="1:25" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
@@ -1029,43 +1024,43 @@
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="W4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="S4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" s="18" t="s">
+      <c r="Y4" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="V4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="W4" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="X4" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y4" s="15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
@@ -1108,136 +1103,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
@@ -9194,136 +9189,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_OW_Part2.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_OW_Part2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gary.cheng_cn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F1CC51-1888-4A50-9A5D-F5B21D936DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2956F13-8A44-4DCF-BA67-CA59E655A5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>Target given to ADM to guide responses</t>
-  </si>
-  <si>
-    <t>Kitware model run on scenario</t>
   </si>
   <si>
     <t>internal tracking identification</t>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t>Tag expectant patient as expectant? N/A - The scenario had no expectant patient</t>
+  </si>
+  <si>
+    <t>Baseline, Zeroshot, DR Mistral or CR Mistral</t>
   </si>
 </sst>
 </file>
@@ -937,84 +937,84 @@
       <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="G3" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="H3" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="I3" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="J3" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="K3" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="L3" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="M3" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="N3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="T3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="12" t="s">
+      <c r="U3" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="12" t="s">
-        <v>41</v>
+      <c r="V3" s="18" t="s">
+        <v>80</v>
       </c>
-      <c r="U3" s="18" t="s">
+      <c r="W3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="18" t="s">
+      <c r="X3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y3" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="W3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" s="7" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
@@ -1024,43 +1024,43 @@
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="12" t="s">
-        <v>48</v>
+      <c r="V4" s="18" t="s">
+        <v>79</v>
       </c>
-      <c r="O4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="U4" s="18" t="s">
+      <c r="W4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="V4" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="W4" s="15" t="s">
+      <c r="X4" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="Y4" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="Y4" s="15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
@@ -1103,136 +1103,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
@@ -9189,136 +9189,136 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>

--- a/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_OW_Part2.xlsx
+++ b/dashboard-ui/src/components/Research/variables/Variable Definitions RQ8_OW_Part2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="95">
   <si>
     <t>Probe</t>
   </si>
@@ -114,6 +114,9 @@
     <t>Alignment score (ADM|target)</t>
   </si>
   <si>
+    <t>Affiliation Value</t>
+  </si>
+  <si>
     <t>AF_attribute</t>
   </si>
   <si>
@@ -121,6 +124,9 @@
   </si>
   <si>
     <t>AF_medical</t>
+  </si>
+  <si>
+    <t>Merit Value</t>
   </si>
   <si>
     <t>MF_attribute</t>
@@ -204,6 +210,9 @@
     <t>Alignment between target and KDMA from probes</t>
   </si>
   <si>
+    <t xml:space="preserve">Affiliation focus midpoint KDMA measurement. Single scalar score. </t>
+  </si>
+  <si>
     <t>Affiliation Focus KDMA measurement from OW sim; attribute term (3 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
   </si>
   <si>
@@ -211,6 +220,9 @@
   </si>
   <si>
     <t>Affiliation Focus KDMA measurement from OW sim; medical urgency term (2 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merit focus midpoint KDMA measurement. Single scalar score. </t>
   </si>
   <si>
     <t>Merit Focus KDMA measurement from OW sim; attribute term (3 of 3 terms in regression approach); TA1 server calculation via probe matcher</t>
@@ -259,16 +271,16 @@
 </t>
   </si>
   <si>
-    <t>MF1-8 or AF1-8</t>
+    <t>MF1-8, AF1-8, ADEPT-June2025-merit-*, ADEPT-June2025-affiliation-*</t>
   </si>
   <si>
     <t>Baseline, Zeroshot, DR Mistral or CR Mistral</t>
   </si>
   <si>
-    <t>Patient A or Patient B</t>
+    <t>0.0-1.0</t>
   </si>
   <si>
-    <t>0.0-1.0</t>
+    <t>Patient A or Patient B</t>
   </si>
   <si>
     <t>Yes, No, N/A</t>
@@ -388,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -423,11 +435,11 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -438,11 +450,8 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
@@ -752,80 +761,82 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="19" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="19" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="19" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="19" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="19" width="25.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="18" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="18" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="18" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="18" width="14.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="18" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="18" width="25.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="19" width="30.290714285714284" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="19" width="28.719285714285714" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="19" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="19" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="10" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="18" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="18" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="18" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="18" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="18" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="18" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="18" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="46.5" customFormat="1" s="11">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="60" customFormat="1" s="11">
       <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>31</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>35</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="12" t="s">
         <v>39</v>
       </c>
       <c r="O1" s="14" t="s">
@@ -846,16 +857,16 @@
       <c r="T1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="W1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X1" s="16" t="s">
+      <c r="X1" s="15" t="s">
         <v>49</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -870,298 +881,326 @@
       <c r="AB1" s="16" t="s">
         <v>53</v>
       </c>
+      <c r="AC1" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD1" s="16" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="33" customFormat="1" s="11">
       <c r="A2" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="17" t="s">
-        <v>55</v>
+      <c r="F2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="G2" s="17" t="s">
-        <v>55</v>
+      <c r="G2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="H2" s="17" t="s">
-        <v>55</v>
+      <c r="H2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="I2" s="17" t="s">
-        <v>55</v>
+      <c r="I2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>55</v>
+      <c r="J2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>55</v>
+      <c r="K2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="L2" s="17" t="s">
-        <v>55</v>
+      <c r="L2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="M2" s="14" t="s">
-        <v>56</v>
+      <c r="M2" s="12" t="s">
+        <v>57</v>
       </c>
-      <c r="N2" s="14" t="s">
-        <v>56</v>
+      <c r="N2" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
-      <c r="U2" s="15" t="s">
-        <v>56</v>
+      <c r="U2" s="14" t="s">
+        <v>58</v>
       </c>
-      <c r="V2" s="15" t="s">
-        <v>56</v>
+      <c r="V2" s="14" t="s">
+        <v>58</v>
       </c>
-      <c r="W2" s="16" t="s">
-        <v>56</v>
+      <c r="W2" s="15" t="s">
+        <v>58</v>
       </c>
-      <c r="X2" s="16" t="s">
-        <v>56</v>
+      <c r="X2" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="Y2" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z2" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AA2" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AB2" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="AC2" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="16" t="s">
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="208.5" customFormat="1" s="11">
       <c r="A3" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="F3" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="G3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="H3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="I3" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="J3" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="K3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="14" t="s">
-        <v>68</v>
+      <c r="L3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="S3" s="14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="T3" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="U3" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="V3" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" s="16" t="s">
+      <c r="X3" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="AA3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="100.5" customFormat="1" s="11">
-      <c r="A4" s="6" t="s">
+      <c r="AA3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="AB3" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="AC3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="AD3" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="14" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="114" customFormat="1" s="11">
+      <c r="A4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="14" t="s">
-        <v>82</v>
+      <c r="B4" s="6" t="s">
+        <v>83</v>
       </c>
+      <c r="C4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
       <c r="O4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="S4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
-      <c r="U4" s="15" t="s">
-        <v>83</v>
+      <c r="U4" s="14" t="s">
+        <v>87</v>
       </c>
-      <c r="V4" s="15" t="s">
-        <v>84</v>
+      <c r="V4" s="14" t="s">
+        <v>87</v>
       </c>
-      <c r="W4" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="X4" s="16" t="s">
+      <c r="W4" s="15" t="s">
         <v>86</v>
       </c>
+      <c r="X4" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="Y4" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Z4" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA4" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AB4" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
+      <c r="AC4" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD4" s="16" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25" customFormat="1" s="11">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25" customFormat="1" s="11">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="18"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
